--- a/气象/蒙古气象/蒙古日常低温阈值记录(蒙古文).xlsx
+++ b/气象/蒙古气象/蒙古日常低温阈值记录(蒙古文).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF735FD-09C7-45B8-8837-BAA8768189C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BB276C-10DD-4D41-8BD3-C3D4695C6C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{6B19DE1B-EB04-49E8-8A38-5AAAD2ACDD71}"/>
   </bookViews>
@@ -336,14 +336,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(蒙古)省</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>今日蒙古气温(℃)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>最低夜温</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -369,6 +361,14 @@
   </si>
   <si>
     <t>台勒门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古气温(℃)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aimag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1019,7 +1019,7 @@
       <c r="B1" s="20"/>
       <c r="C1" s="21"/>
       <c r="D1" s="22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1" s="23"/>
       <c r="F1" s="23"/>
@@ -1032,7 +1032,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="17" t="s">
@@ -1040,16 +1040,16 @@
       </c>
       <c r="E2" s="17"/>
       <c r="F2" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -1802,7 +1802,7 @@
         <v>-27.7</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I36" s="5"/>
     </row>
@@ -1910,7 +1910,7 @@
         <v>63</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5">
@@ -2000,7 +2000,7 @@
         <v>68</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5">
